--- a/Employee_Reports_wi52/Kevin Carl Enriquez Serrano Q0604.xlsx
+++ b/Employee_Reports_wi52/Kevin Carl Enriquez Serrano Q0604.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1068,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1117,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1166,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-29</v>
+        <v>-37</v>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1215,11 +1215,11 @@
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-23</v>
+        <v>-31</v>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1264,11 +1264,11 @@
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-23</v>
+        <v>-31</v>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1301,11 +1301,11 @@
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-14</v>
+        <v>-22</v>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1350,11 +1350,11 @@
         </is>
       </c>
       <c r="H19" s="5" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
@@ -1399,11 +1399,11 @@
         </is>
       </c>
       <c r="H20" s="5" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
@@ -1436,11 +1436,11 @@
         </is>
       </c>
       <c r="H21" s="5" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
@@ -1485,11 +1485,11 @@
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1498,6 +1498,43 @@
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IS0 55001 (Other Trainings)</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr"/>
+      <c r="D23" s="3" t="inlineStr"/>
+      <c r="E23" s="3" t="inlineStr"/>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>24-Aug-2026</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>23-Aug-2028</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="n">
+        <v>726</v>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1978,7 +2015,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7907</v>
+        <v>7899</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2073,7 +2110,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7895</v>
+        <v>7887</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2102,7 +2139,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7895</v>
+        <v>7887</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -2131,7 +2168,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7898</v>
+        <v>7890</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -2160,7 +2197,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7898</v>
+        <v>7890</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -2189,7 +2226,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7923</v>
+        <v>7915</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -2218,7 +2255,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7923</v>
+        <v>7915</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -2247,7 +2284,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7923</v>
+        <v>7915</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -2276,7 +2313,7 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7969</v>
+        <v>7961</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -2305,7 +2342,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>7969</v>
+        <v>7961</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -2334,7 +2371,7 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7969</v>
+        <v>7961</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -2363,7 +2400,7 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7969</v>
+        <v>7961</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -2392,7 +2429,7 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7969</v>
+        <v>7961</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -2421,7 +2458,7 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7923</v>
+        <v>7915</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -2450,7 +2487,7 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>7923</v>
+        <v>7915</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -2479,7 +2516,7 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>7975</v>
+        <v>7967</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -2508,7 +2545,7 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>7975</v>
+        <v>7967</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -2537,7 +2574,7 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>7975</v>
+        <v>7967</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -2566,7 +2603,7 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>7975</v>
+        <v>7967</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -2595,7 +2632,7 @@
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>7975</v>
+        <v>7967</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
